--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП Луганск на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП Луганск на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7B8F68-1C6F-4AF1-ABD6-115A65C2886C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBF4CA-D398-4D9D-8023-97EF409A0801}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="224">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -995,6 +995,15 @@
   </si>
   <si>
     <t>ПОСОЛЬСКАЯ ПМ с/к с/н в/у 1/100 10шт</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> БАВАРСКИЕ ПМ сос ц/о мгс 0.35кг 8шт.</t>
+  </si>
+  <si>
+    <t>ЛП Малахутин (Донецк)</t>
   </si>
 </sst>
 </file>
@@ -6265,7 +6274,12 @@
       <c r="H3" s="134"/>
       <c r="I3" s="134"/>
       <c r="J3" s="135"/>
-      <c r="K3" s="101"/>
+      <c r="K3" s="101">
+        <v>130439106</v>
+      </c>
+      <c r="L3" s="99" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="4" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="K4" s="101"/>
@@ -7784,16 +7798,16 @@
     <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="123" t="str">
         <f t="shared" si="1"/>
-        <v>6353</v>
+        <v>7632</v>
       </c>
       <c r="B27" s="53" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="C27" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="51">
-        <v>1001012506353</v>
+        <v>1001012507632</v>
       </c>
       <c r="E27" s="24"/>
       <c r="F27" s="124">
@@ -8723,7 +8737,7 @@
         <v>6602</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="C38" s="50" t="s">
         <v>20</v>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП Луганск на .xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП Луганск на .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DBF4CA-D398-4D9D-8023-97EF409A0801}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424DD3F3-EF37-426F-A455-CC2F1901FAD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$162</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$598</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$164</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$600</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$600</definedName>
   </definedNames>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="226">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1004,6 +1004,12 @@
   </si>
   <si>
     <t>ЛП Малахутин (Донецк)</t>
+  </si>
+  <si>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
   </si>
 </sst>
 </file>
@@ -6205,7 +6211,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1686"/>
+  <dimension ref="A1:BO1688"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -12405,7 +12411,7 @@
     </row>
     <row r="81" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A81" s="123" t="str">
-        <f t="shared" ref="A81:A103" si="16">RIGHT(D81,4)</f>
+        <f t="shared" ref="A81:A104" si="16">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
       <c r="B81" s="53" t="s">
@@ -12510,7 +12516,7 @@
         <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" ref="G82:G92" si="17">E82*F82</f>
+        <f t="shared" ref="G82:G93" si="17">E82*F82</f>
         <v>0</v>
       </c>
       <c r="H82" s="14">
@@ -13356,31 +13362,27 @@
     <row r="92" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>6787</v>
-      </c>
-      <c r="B92" s="127" t="s">
-        <v>65</v>
+        <v>7489</v>
+      </c>
+      <c r="B92" s="53" t="s">
+        <v>224</v>
       </c>
       <c r="C92" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="51">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G92" si="18">E92*F92</f>
         <v>0</v>
       </c>
-      <c r="H92" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I92" s="14">
-        <v>45</v>
-      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="29"/>
       <c r="L92"/>
       <c r="M92"/>
@@ -13442,30 +13444,30 @@
     <row r="93" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7166</v>
+        <v>6787</v>
       </c>
       <c r="B93" s="127" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C93" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D93" s="51">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G93" s="23">
-        <f>E93</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I93" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J93" s="29"/>
       <c r="L93"/>
@@ -13525,30 +13527,30 @@
       <c r="BN93"/>
       <c r="BO93"/>
     </row>
-    <row r="94" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7169</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>70</v>
+        <v>7166</v>
+      </c>
+      <c r="B94" s="127" t="s">
+        <v>71</v>
       </c>
       <c r="C94" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D94" s="51">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G94" s="23">
-        <f>E94*F94</f>
+        <f>E94</f>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I94" s="14">
         <v>50</v>
@@ -13614,32 +13616,32 @@
     <row r="95" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>5544</v>
+        <v>7169</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C95" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D95" s="51">
-        <v>1001051875544</v>
+        <v>1001303987169</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G95" s="23">
-        <f>E95</f>
+        <f>E95*F95</f>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>4.8600000000000003</v>
+        <v>2.8</v>
       </c>
       <c r="I95" s="14">
-        <v>45</v>
-      </c>
-      <c r="J95" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J95" s="29"/>
       <c r="L95"/>
       <c r="M95"/>
       <c r="N95"/>
@@ -13700,27 +13702,27 @@
     <row r="96" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>6697</v>
+        <v>5544</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C96" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D96" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" ref="G96:G103" si="18">E96*F96</f>
+        <f>E96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I96" s="14">
         <v>45</v>
@@ -13786,27 +13788,27 @@
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7237</v>
+        <v>6697</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="51">
-        <v>1001304497237</v>
+        <v>1001301876697</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G97:G104" si="19">E97*F97</f>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
         <v>45</v>
@@ -13872,27 +13874,27 @@
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7238</v>
+        <v>7237</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="51">
-        <v>1001305197238</v>
+        <v>1001304497237</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I98" s="14">
         <v>45</v>
@@ -13958,30 +13960,30 @@
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7177</v>
+        <v>7238</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="51">
-        <v>1001302347177</v>
+        <v>1001305197238</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I99" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J99" s="49"/>
       <c r="L99"/>
@@ -14044,27 +14046,27 @@
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I100" s="14">
         <v>50</v>
@@ -14130,23 +14132,23 @@
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G101" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
@@ -14216,30 +14218,30 @@
     <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>6459</v>
+        <v>7333</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="51">
-        <v>1001214196459</v>
+        <v>1001303987333</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H102" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I102" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J102" s="49"/>
       <c r="L102"/>
@@ -14299,26 +14301,26 @@
       <c r="BN102"/>
       <c r="BO102"/>
     </row>
-    <row r="103" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="123" t="str">
         <f t="shared" si="16"/>
-        <v>7474</v>
+        <v>6459</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="51">
-        <v>1001216717474</v>
+        <v>1001214196459</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
         <v>0.1</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
@@ -14385,21 +14387,35 @@
       <c r="BN103"/>
       <c r="BO103"/>
     </row>
-    <row r="104" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B104" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C104" s="42"/>
-      <c r="D104" s="42"/>
+    <row r="104" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="123" t="str">
+        <f t="shared" si="16"/>
+        <v>7474</v>
+      </c>
+      <c r="B104" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C104" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104" s="51">
+        <v>1001216717474</v>
+      </c>
       <c r="E104" s="24"/>
-      <c r="F104" s="41"/>
-      <c r="G104" s="42"/>
-      <c r="H104" s="42"/>
-      <c r="I104" s="42"/>
-      <c r="J104" s="43"/>
+      <c r="F104" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G104" s="23">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="H104" s="14">
+        <v>1</v>
+      </c>
+      <c r="I104" s="14">
+        <v>45</v>
+      </c>
+      <c r="J104" s="49"/>
       <c r="L104"/>
       <c r="M104"/>
       <c r="N104"/>
@@ -14457,35 +14473,21 @@
       <c r="BN104"/>
       <c r="BO104"/>
     </row>
-    <row r="105" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="123" t="str">
-        <f t="shared" ref="A105:A138" si="19">RIGHT(D105,4)</f>
-        <v>3582</v>
-      </c>
-      <c r="B105" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C105" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D105" s="51">
-        <v>1001061973582</v>
-      </c>
+    <row r="105" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
       <c r="E105" s="24"/>
-      <c r="F105" s="124">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G105" s="23">
-        <f>E105</f>
-        <v>0</v>
-      </c>
-      <c r="H105" s="128">
-        <v>3.9</v>
-      </c>
-      <c r="I105" s="129">
-        <v>120</v>
-      </c>
-      <c r="J105" s="29"/>
+      <c r="F105" s="41"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+      <c r="I105" s="42"/>
+      <c r="J105" s="43"/>
       <c r="L105"/>
       <c r="M105"/>
       <c r="N105"/>
@@ -14543,30 +14545,30 @@
       <c r="BN105"/>
       <c r="BO105"/>
     </row>
-    <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A106" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>3986</v>
+        <f t="shared" ref="A106:A139" si="20">RIGHT(D106,4)</f>
+        <v>3582</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D106" s="51">
-        <v>1001061973986</v>
+        <v>1001061973582</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="124">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" ref="G106:G111" si="20">E106*F106</f>
+        <f>E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="128">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I106" s="129">
         <v>120</v>
@@ -14631,30 +14633,30 @@
     </row>
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>5931</v>
+        <f t="shared" si="20"/>
+        <v>3986</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D107" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E107" s="24"/>
-      <c r="F107" s="23">
-        <v>0.22</v>
+      <c r="F107" s="124">
+        <v>0.25</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G107:G112" si="21">E107*F107</f>
         <v>0</v>
       </c>
-      <c r="H107" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I107" s="14">
+      <c r="H107" s="128">
+        <v>2</v>
+      </c>
+      <c r="I107" s="129">
         <v>120</v>
       </c>
       <c r="J107" s="29"/>
@@ -14717,28 +14719,28 @@
     </row>
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>5708</v>
+        <f t="shared" si="20"/>
+        <v>5931</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D108" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" ref="G108:G109" si="21">E108</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H108" s="14">
-        <v>4</v>
+      <c r="H108" s="97">
+        <v>1.76</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -14803,28 +14805,28 @@
     </row>
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>3287</v>
+        <f t="shared" si="20"/>
+        <v>5708</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D109" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G109:G110" si="22">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -14889,28 +14891,28 @@
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>4993</v>
+        <f t="shared" si="20"/>
+        <v>3287</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -14975,24 +14977,24 @@
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>5483</v>
+        <f t="shared" si="20"/>
+        <v>4993</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
         <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
@@ -15061,28 +15063,28 @@
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>4117</v>
+        <f t="shared" si="20"/>
+        <v>5483</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D112" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" ref="G112:G113" si="22">E112</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -15147,28 +15149,28 @@
     </row>
     <row r="113" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>0614</v>
+        <f t="shared" si="20"/>
+        <v>4117</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D113" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G113:G114" si="23">E113</f>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -15233,28 +15235,28 @@
     </row>
     <row r="114" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6967</v>
+        <f t="shared" si="20"/>
+        <v>0614</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C114" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" ref="G114:G124" si="23">E114*F114</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -15319,24 +15321,24 @@
     </row>
     <row r="115" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6937</v>
+        <f t="shared" si="20"/>
+        <v>6967</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
         <v>0.25</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G115:G125" si="24">E115*F115</f>
         <v>0</v>
       </c>
       <c r="H115" s="14">
@@ -15405,28 +15407,28 @@
     </row>
     <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7143</v>
+        <f t="shared" si="20"/>
+        <v>6937</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I116" s="14">
         <v>120</v>
@@ -15491,24 +15493,24 @@
     </row>
     <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7147</v>
+        <f t="shared" si="20"/>
+        <v>7143</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
         <v>0.22</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
@@ -15577,31 +15579,31 @@
     </row>
     <row r="118" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7456</v>
+        <f t="shared" si="20"/>
+        <v>7147</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I118" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118"/>
@@ -15663,28 +15665,28 @@
     </row>
     <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7364</v>
+        <f t="shared" si="20"/>
+        <v>7456</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I119" s="14">
         <v>90</v>
@@ -15749,24 +15751,24 @@
     </row>
     <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7383</v>
+        <f t="shared" si="20"/>
+        <v>7364</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
         <v>0.22</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
@@ -15835,31 +15837,31 @@
     </row>
     <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7317</v>
+        <f t="shared" si="20"/>
+        <v>7383</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I121" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121"/>
@@ -15921,28 +15923,28 @@
     </row>
     <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7318</v>
+        <f t="shared" si="20"/>
+        <v>7317</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I122" s="14">
         <v>120</v>
@@ -16007,28 +16009,28 @@
     </row>
     <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7316</v>
+        <f t="shared" si="20"/>
+        <v>7318</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I123" s="14">
         <v>120</v>
@@ -16093,31 +16095,31 @@
     </row>
     <row r="124" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7417</v>
+        <f t="shared" si="20"/>
+        <v>7316</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001307147417</v>
+        <v>1001060727316</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I124" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J124" s="29"/>
       <c r="L124"/>
@@ -16179,31 +16181,31 @@
     </row>
     <row r="125" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6832</v>
+        <f t="shared" si="20"/>
+        <v>7417</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D125" s="51">
-        <v>1001065616832</v>
+        <v>1001307147417</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.215</v>
+        <v>0.44</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" ref="G125:G126" si="24">E125</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I125" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J125" s="29"/>
       <c r="L125"/>
@@ -16265,24 +16267,24 @@
     </row>
     <row r="126" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7299</v>
+        <f t="shared" si="20"/>
+        <v>6832</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D126" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
         <v>0.215</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G126:G127" si="25">E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
@@ -16351,31 +16353,31 @@
     </row>
     <row r="127" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7386</v>
+        <f t="shared" si="20"/>
+        <v>7299</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D127" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" ref="G127:G137" si="25">E127*F127</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I127" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J127" s="29"/>
       <c r="L127"/>
@@ -16437,31 +16439,31 @@
     </row>
     <row r="128" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6454</v>
+        <f t="shared" si="20"/>
+        <v>7386</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>211</v>
+        <v>150</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="51">
-        <v>1001201976454</v>
+        <v>1001067017386</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G128:G138" si="26">E128*F128</f>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I128" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J128" s="29"/>
       <c r="L128"/>
@@ -16523,24 +16525,24 @@
     </row>
     <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6834</v>
+        <f t="shared" si="20"/>
+        <v>6454</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001203146834</v>
+        <v>1001201976454</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
         <v>0.1</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
@@ -16609,28 +16611,28 @@
     </row>
     <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7382</v>
+        <f t="shared" si="20"/>
+        <v>6834</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D130" s="51">
-        <v>1001203117382</v>
+        <v>1001203146834</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
@@ -16695,28 +16697,28 @@
     </row>
     <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6453</v>
+        <f t="shared" si="20"/>
+        <v>7382</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>212</v>
+        <v>84</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D131" s="51">
-        <v>1001202506453</v>
+        <v>1001203117382</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
@@ -16781,28 +16783,28 @@
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6221</v>
+        <f t="shared" si="20"/>
+        <v>6453</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>86</v>
+        <v>212</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D132" s="51">
-        <v>1001205376221</v>
+        <v>1001202506453</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
@@ -16867,24 +16869,24 @@
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6222</v>
+        <f t="shared" si="20"/>
+        <v>6221</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
         <v>0.09</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
@@ -16953,28 +16955,28 @@
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6965</v>
+        <f t="shared" si="20"/>
+        <v>6222</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -17039,28 +17041,28 @@
     </row>
     <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>6557</v>
+        <f t="shared" si="20"/>
+        <v>6965</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D135" s="51">
-        <v>1001200756557</v>
+        <v>1001206356965</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H135" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I135" s="14">
         <v>60</v>
@@ -17125,28 +17127,28 @@
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>5679</v>
+        <f t="shared" si="20"/>
+        <v>6557</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D136" s="51">
-        <v>1001190765679</v>
+        <v>1001200756557</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G136" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
@@ -17211,28 +17213,28 @@
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>5677</v>
+        <f t="shared" si="20"/>
+        <v>5679</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="51">
-        <v>1001190715677</v>
+        <v>1001190765679</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -17295,30 +17297,30 @@
       <c r="BN137"/>
       <c r="BO137"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="123" t="str">
-        <f t="shared" si="19"/>
-        <v>7414</v>
+        <f t="shared" si="20"/>
+        <v>5677</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D138" s="51">
-        <v>1001204447414</v>
+        <v>1001190715677</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G138" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H138" s="14">
         <v>1</v>
-      </c>
-      <c r="G138" s="23">
-        <f>E138</f>
-        <v>0</v>
-      </c>
-      <c r="H138" s="14">
-        <v>8</v>
       </c>
       <c r="I138" s="14">
         <v>60</v>
@@ -17381,21 +17383,35 @@
       <c r="BN138"/>
       <c r="BO138"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B139" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="123" t="str">
+        <f t="shared" si="20"/>
+        <v>7414</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D139" s="51">
+        <v>1001204447414</v>
+      </c>
       <c r="E139" s="24"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
+      <c r="F139" s="23">
+        <v>1</v>
+      </c>
+      <c r="G139" s="23">
+        <f>E139</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
+        <v>8</v>
+      </c>
+      <c r="I139" s="14">
+        <v>60</v>
+      </c>
+      <c r="J139" s="29"/>
       <c r="L139"/>
       <c r="M139"/>
       <c r="N139"/>
@@ -17453,35 +17469,21 @@
       <c r="BN139"/>
       <c r="BO139"/>
     </row>
-    <row r="140" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="123" t="str">
-        <f t="shared" ref="A140:A149" si="26">RIGHT(D140,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B140" s="98" t="s">
-        <v>213</v>
-      </c>
-      <c r="C140" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="130">
-        <v>1001092674584</v>
-      </c>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B140" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
       <c r="E140" s="24"/>
-      <c r="F140" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="G140" s="23">
-        <f>E140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I140" s="14">
-        <v>60</v>
-      </c>
-      <c r="J140" s="29"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
       <c r="L140"/>
       <c r="M140"/>
       <c r="N140"/>
@@ -17539,33 +17541,33 @@
       <c r="BN140"/>
       <c r="BO140"/>
     </row>
-    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A141" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>6495</v>
+        <f t="shared" ref="A141:A150" si="27">RIGHT(D141,4)</f>
+        <v>4584</v>
       </c>
       <c r="B141" s="98" t="s">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D141" s="51">
-        <v>1001092436495</v>
+        <v>22</v>
+      </c>
+      <c r="D141" s="130">
+        <v>1001092674584</v>
       </c>
       <c r="E141" s="24"/>
-      <c r="F141" s="124">
-        <v>0.3</v>
+      <c r="F141" s="23">
+        <v>2.5</v>
       </c>
       <c r="G141" s="23">
-        <f>E141*F141</f>
+        <f>E141</f>
         <v>0</v>
       </c>
-      <c r="H141" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I141" s="29">
-        <v>45</v>
+      <c r="H141" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I141" s="14">
+        <v>60</v>
       </c>
       <c r="J141" s="29"/>
       <c r="L141"/>
@@ -17627,28 +17629,28 @@
     </row>
     <row r="142" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>6470</v>
-      </c>
-      <c r="B142" s="131" t="s">
-        <v>116</v>
+        <f t="shared" si="27"/>
+        <v>6495</v>
+      </c>
+      <c r="B142" s="98" t="s">
+        <v>95</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="124">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" ref="G142:G143" si="27">E142</f>
+        <f>E142*F142</f>
         <v>0</v>
       </c>
       <c r="H142" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I142" s="29">
         <v>45</v>
@@ -17713,31 +17715,31 @@
     </row>
     <row r="143" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>5452</v>
+        <f t="shared" si="27"/>
+        <v>6470</v>
       </c>
       <c r="B143" s="131" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C143" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="124">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G143:G144" si="28">E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I143" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J143" s="29"/>
       <c r="L143"/>
@@ -17799,28 +17801,28 @@
     </row>
     <row r="144" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>3215</v>
+        <f t="shared" si="27"/>
+        <v>5452</v>
       </c>
       <c r="B144" s="131" t="s">
-        <v>214</v>
+        <v>93</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D144" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="124">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G144" s="23">
-        <f>E144*F144</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H144" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I144" s="29">
         <v>60</v>
@@ -17885,28 +17887,28 @@
     </row>
     <row r="145" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>6866</v>
+        <f t="shared" si="27"/>
+        <v>3215</v>
       </c>
       <c r="B145" s="131" t="s">
-        <v>92</v>
+        <v>214</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D145" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="124">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G145" s="23">
-        <f>E145</f>
+        <f>E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I145" s="29">
         <v>60</v>
@@ -17969,30 +17971,30 @@
       <c r="BN145"/>
       <c r="BO145"/>
     </row>
-    <row r="146" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>5495</v>
-      </c>
-      <c r="B146" s="53" t="s">
-        <v>94</v>
+        <f t="shared" si="27"/>
+        <v>6866</v>
+      </c>
+      <c r="B146" s="131" t="s">
+        <v>92</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="132">
-        <v>1001093345495</v>
+        <v>22</v>
+      </c>
+      <c r="D146" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="124">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" ref="G146:G148" si="28">E146*F146</f>
+        <f>E146</f>
         <v>0</v>
       </c>
       <c r="H146" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I146" s="29">
         <v>60</v>
@@ -18057,31 +18059,31 @@
     </row>
     <row r="147" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>7377</v>
+        <f t="shared" si="27"/>
+        <v>5495</v>
       </c>
       <c r="B147" s="53" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C147" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="132">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="124">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G147:G149" si="29">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I147" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J147" s="29"/>
       <c r="L147"/>
@@ -18143,28 +18145,28 @@
     </row>
     <row r="148" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>6925</v>
+        <f t="shared" si="27"/>
+        <v>7377</v>
       </c>
       <c r="B148" s="53" t="s">
-        <v>215</v>
+        <v>117</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="132">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="124">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H148" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="29">
         <v>45</v>
@@ -18227,33 +18229,33 @@
       <c r="BN148"/>
       <c r="BO148"/>
     </row>
-    <row r="149" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="123" t="str">
-        <f t="shared" si="26"/>
-        <v>6025</v>
+        <f t="shared" si="27"/>
+        <v>6925</v>
       </c>
       <c r="B149" s="53" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D149" s="132">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="124">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G149" s="23">
-        <f>E149</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H149" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I149" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J149" s="29"/>
       <c r="L149"/>
@@ -18313,21 +18315,35 @@
       <c r="BN149"/>
       <c r="BO149"/>
     </row>
-    <row r="150" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B150" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C150" s="42"/>
-      <c r="D150" s="42"/>
+    <row r="150" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="123" t="str">
+        <f t="shared" si="27"/>
+        <v>6025</v>
+      </c>
+      <c r="B150" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="C150" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D150" s="132">
+        <v>1001094966025</v>
+      </c>
       <c r="E150" s="24"/>
-      <c r="F150" s="41"/>
-      <c r="G150" s="42"/>
-      <c r="H150" s="42"/>
-      <c r="I150" s="42"/>
-      <c r="J150" s="43"/>
+      <c r="F150" s="124">
+        <v>3</v>
+      </c>
+      <c r="G150" s="23">
+        <f>E150</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="29">
+        <v>6</v>
+      </c>
+      <c r="I150" s="29">
+        <v>60</v>
+      </c>
+      <c r="J150" s="29"/>
       <c r="L150"/>
       <c r="M150"/>
       <c r="N150"/>
@@ -18385,35 +18401,21 @@
       <c r="BN150"/>
       <c r="BO150"/>
     </row>
-    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="123" t="str">
-        <f t="shared" ref="A151:A161" si="29">RIGHT(D151,4)</f>
-        <v>7090</v>
-      </c>
-      <c r="B151" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D151" s="51">
-        <v>1001084217090</v>
-      </c>
+    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B151" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C151" s="42"/>
+      <c r="D151" s="42"/>
       <c r="E151" s="24"/>
-      <c r="F151" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G151" s="23">
-        <f t="shared" ref="G151:G152" si="30">E151*F151</f>
-        <v>0</v>
-      </c>
-      <c r="H151" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I151" s="14">
-        <v>50</v>
-      </c>
-      <c r="J151" s="29"/>
+      <c r="F151" s="41"/>
+      <c r="G151" s="42"/>
+      <c r="H151" s="42"/>
+      <c r="I151" s="42"/>
+      <c r="J151" s="43"/>
       <c r="L151"/>
       <c r="M151"/>
       <c r="N151"/>
@@ -18471,26 +18473,26 @@
       <c r="BN151"/>
       <c r="BO151"/>
     </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A152" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>7187</v>
+        <f t="shared" ref="A152:A163" si="30">RIGHT(D152,4)</f>
+        <v>7090</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C152" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
         <v>0.3</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G152:G153" si="31">E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
@@ -18559,31 +18561,31 @@
     </row>
     <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6620</v>
+        <f t="shared" si="30"/>
+        <v>7187</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D153" s="51">
-        <v>1001081596620</v>
+        <v>1001085637187</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G153" s="23">
-        <f>E153</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I153" s="14">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J153" s="29"/>
       <c r="L153"/>
@@ -18645,31 +18647,31 @@
     </row>
     <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>7103</v>
+        <f t="shared" si="30"/>
+        <v>6620</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D154" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" ref="G154:G161" si="31">E154*F154</f>
+        <f>E154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I154" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J154" s="29"/>
       <c r="L154"/>
@@ -18731,32 +18733,26 @@
     </row>
     <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="123" t="str">
-        <f>RIGHT(D155,4)</f>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>6008</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D155" s="51">
-        <v>1001223297092</v>
+        <v>1001084856008</v>
       </c>
       <c r="E155" s="24"/>
-      <c r="F155" s="23">
-        <v>0.14000000000000001</v>
-      </c>
+      <c r="F155" s="23"/>
       <c r="G155" s="23">
-        <f t="shared" si="31"/>
+        <f>E155</f>
         <v>0</v>
       </c>
-      <c r="H155" s="14">
-        <v>1.4</v>
-      </c>
-      <c r="I155" s="14">
-        <v>50</v>
-      </c>
+      <c r="H155" s="14"/>
+      <c r="I155" s="14"/>
       <c r="J155" s="29"/>
       <c r="L155"/>
       <c r="M155"/>
@@ -18817,31 +18813,31 @@
     </row>
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6228</v>
+        <f t="shared" si="30"/>
+        <v>7103</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001225416228</v>
+        <v>1001223297103</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G156:G163" si="32">E156*F156</f>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I156" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J156" s="29"/>
       <c r="L156"/>
@@ -18903,31 +18899,31 @@
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6448</v>
+        <f>RIGHT(D157,4)</f>
+        <v>7092</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="51">
-        <v>1001234146448</v>
+        <v>1001223297092</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.1</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="I157" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J157" s="29"/>
       <c r="L157"/>
@@ -18989,28 +18985,28 @@
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6208</v>
+        <f t="shared" si="30"/>
+        <v>6228</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220226208</v>
+        <v>1001225416228</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="I158" s="14">
         <v>45</v>
@@ -19075,31 +19071,31 @@
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6754</v>
+        <f t="shared" si="30"/>
+        <v>6448</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225406754</v>
+        <v>1001234146448</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="I159" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J159" s="29"/>
       <c r="L159"/>
@@ -19161,28 +19157,28 @@
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>6279</v>
+        <f t="shared" si="30"/>
+        <v>6208</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220286279</v>
+        <v>1001220226208</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
         <v>0.15</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -19245,30 +19241,30 @@
       <c r="BN160"/>
       <c r="BO160"/>
     </row>
-    <row r="161" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="123" t="str">
-        <f t="shared" si="29"/>
-        <v>7288</v>
+        <f t="shared" si="30"/>
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D161" s="51">
-        <v>1001223907288</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
         <v>60</v>
@@ -19331,25 +19327,35 @@
       <c r="BN161"/>
       <c r="BO161"/>
     </row>
-    <row r="162" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="48"/>
-      <c r="B162" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C162" s="16"/>
-      <c r="D162" s="36"/>
-      <c r="E162" s="17">
-        <f>SUM(E10:E161)</f>
+    <row r="162" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="123" t="str">
+        <f t="shared" si="30"/>
+        <v>6279</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C162" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D162" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G162" s="23">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="F162" s="17"/>
-      <c r="G162" s="17">
-        <f>SUM(G11:G161)</f>
-        <v>0</v>
-      </c>
-      <c r="H162" s="17"/>
-      <c r="I162" s="17"/>
-      <c r="J162" s="17"/>
+      <c r="H162" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I162" s="14">
+        <v>45</v>
+      </c>
+      <c r="J162" s="29"/>
       <c r="L162"/>
       <c r="M162"/>
       <c r="N162"/>
@@ -19407,27 +19413,169 @@
       <c r="BN162"/>
       <c r="BO162"/>
     </row>
-    <row r="163" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="37"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="40"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="164" spans="1:67" x14ac:dyDescent="0.25">
-      <c r="B164" s="37"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="40"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="21"/>
-    </row>
-    <row r="165" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="123" t="str">
+        <f t="shared" si="30"/>
+        <v>7288</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C163" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" s="51">
+        <v>1001223907288</v>
+      </c>
+      <c r="E163" s="24"/>
+      <c r="F163" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G163" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H163" s="14">
+        <v>1</v>
+      </c>
+      <c r="I163" s="14">
+        <v>60</v>
+      </c>
+      <c r="J163" s="29"/>
+      <c r="L163"/>
+      <c r="M163"/>
+      <c r="N163"/>
+      <c r="O163"/>
+      <c r="P163"/>
+      <c r="Q163"/>
+      <c r="R163"/>
+      <c r="S163"/>
+      <c r="T163"/>
+      <c r="U163"/>
+      <c r="V163"/>
+      <c r="W163"/>
+      <c r="X163"/>
+      <c r="Y163"/>
+      <c r="Z163"/>
+      <c r="AA163"/>
+      <c r="AB163"/>
+      <c r="AC163"/>
+      <c r="AD163"/>
+      <c r="AE163"/>
+      <c r="AF163"/>
+      <c r="AG163"/>
+      <c r="AH163"/>
+      <c r="AI163"/>
+      <c r="AJ163"/>
+      <c r="AK163"/>
+      <c r="AL163"/>
+      <c r="AM163"/>
+      <c r="AN163"/>
+      <c r="AO163"/>
+      <c r="AP163"/>
+      <c r="AQ163"/>
+      <c r="AR163"/>
+      <c r="AS163"/>
+      <c r="AT163"/>
+      <c r="AU163"/>
+      <c r="AV163"/>
+      <c r="AW163"/>
+      <c r="AX163"/>
+      <c r="AY163"/>
+      <c r="AZ163"/>
+      <c r="BA163"/>
+      <c r="BB163"/>
+      <c r="BC163"/>
+      <c r="BD163"/>
+      <c r="BE163"/>
+      <c r="BF163"/>
+      <c r="BG163"/>
+      <c r="BH163"/>
+      <c r="BI163"/>
+      <c r="BJ163"/>
+      <c r="BK163"/>
+      <c r="BL163"/>
+      <c r="BM163"/>
+      <c r="BN163"/>
+      <c r="BO163"/>
+    </row>
+    <row r="164" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="48"/>
+      <c r="B164" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C164" s="16"/>
+      <c r="D164" s="36"/>
+      <c r="E164" s="17">
+        <f>SUM(E10:E163)</f>
+        <v>0</v>
+      </c>
+      <c r="F164" s="17"/>
+      <c r="G164" s="17">
+        <f>SUM(G11:G163)</f>
+        <v>0</v>
+      </c>
+      <c r="H164" s="17"/>
+      <c r="I164" s="17"/>
+      <c r="J164" s="17"/>
+      <c r="L164"/>
+      <c r="M164"/>
+      <c r="N164"/>
+      <c r="O164"/>
+      <c r="P164"/>
+      <c r="Q164"/>
+      <c r="R164"/>
+      <c r="S164"/>
+      <c r="T164"/>
+      <c r="U164"/>
+      <c r="V164"/>
+      <c r="W164"/>
+      <c r="X164"/>
+      <c r="Y164"/>
+      <c r="Z164"/>
+      <c r="AA164"/>
+      <c r="AB164"/>
+      <c r="AC164"/>
+      <c r="AD164"/>
+      <c r="AE164"/>
+      <c r="AF164"/>
+      <c r="AG164"/>
+      <c r="AH164"/>
+      <c r="AI164"/>
+      <c r="AJ164"/>
+      <c r="AK164"/>
+      <c r="AL164"/>
+      <c r="AM164"/>
+      <c r="AN164"/>
+      <c r="AO164"/>
+      <c r="AP164"/>
+      <c r="AQ164"/>
+      <c r="AR164"/>
+      <c r="AS164"/>
+      <c r="AT164"/>
+      <c r="AU164"/>
+      <c r="AV164"/>
+      <c r="AW164"/>
+      <c r="AX164"/>
+      <c r="AY164"/>
+      <c r="AZ164"/>
+      <c r="BA164"/>
+      <c r="BB164"/>
+      <c r="BC164"/>
+      <c r="BD164"/>
+      <c r="BE164"/>
+      <c r="BF164"/>
+      <c r="BG164"/>
+      <c r="BH164"/>
+      <c r="BI164"/>
+      <c r="BJ164"/>
+      <c r="BK164"/>
+      <c r="BL164"/>
+      <c r="BM164"/>
+      <c r="BN164"/>
+      <c r="BO164"/>
+    </row>
+    <row r="165" spans="1:67" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
       <c r="C165" s="18"/>
       <c r="D165" s="40"/>
@@ -19469,55 +19617,55 @@
     </row>
     <row r="169" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B169" s="37"/>
-      <c r="C169" s="55"/>
-      <c r="D169" s="56"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="58"/>
-      <c r="G169" s="58"/>
-      <c r="H169" s="59"/>
-      <c r="I169" s="59"/>
+      <c r="C169" s="18"/>
+      <c r="D169" s="40"/>
+      <c r="F169" s="19"/>
+      <c r="G169" s="19"/>
+      <c r="H169" s="20"/>
+      <c r="I169" s="20"/>
       <c r="J169" s="21"/>
     </row>
     <row r="170" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B170" s="37"/>
-      <c r="C170" s="55"/>
-      <c r="D170" s="56"/>
-      <c r="E170" s="57"/>
-      <c r="F170" s="58"/>
-      <c r="G170" s="58"/>
-      <c r="H170" s="59"/>
-      <c r="I170" s="59"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="40"/>
+      <c r="F170" s="19"/>
+      <c r="G170" s="19"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="20"/>
       <c r="J170" s="21"/>
     </row>
     <row r="171" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="55"/>
-      <c r="D171" s="60"/>
-      <c r="E171" s="61"/>
-      <c r="F171" s="60"/>
-      <c r="G171" s="62"/>
-      <c r="H171" s="63"/>
-      <c r="I171" s="64"/>
+      <c r="D171" s="56"/>
+      <c r="E171" s="57"/>
+      <c r="F171" s="58"/>
+      <c r="G171" s="58"/>
+      <c r="H171" s="59"/>
+      <c r="I171" s="59"/>
       <c r="J171" s="21"/>
     </row>
     <row r="172" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
-      <c r="C172" s="18"/>
-      <c r="D172" s="40"/>
-      <c r="F172" s="19"/>
-      <c r="G172" s="19"/>
-      <c r="H172" s="20"/>
-      <c r="I172" s="20"/>
+      <c r="C172" s="55"/>
+      <c r="D172" s="56"/>
+      <c r="E172" s="57"/>
+      <c r="F172" s="58"/>
+      <c r="G172" s="58"/>
+      <c r="H172" s="59"/>
+      <c r="I172" s="59"/>
       <c r="J172" s="21"/>
     </row>
     <row r="173" spans="1:67" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="40"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
+      <c r="C173" s="55"/>
+      <c r="D173" s="60"/>
+      <c r="E173" s="61"/>
+      <c r="F173" s="60"/>
+      <c r="G173" s="62"/>
+      <c r="H173" s="63"/>
+      <c r="I173" s="64"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:67" x14ac:dyDescent="0.25">
@@ -34650,13 +34798,33 @@
       <c r="I1686" s="20"/>
       <c r="J1686" s="21"/>
     </row>
+    <row r="1687" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1687" s="37"/>
+      <c r="C1687" s="18"/>
+      <c r="D1687" s="40"/>
+      <c r="F1687" s="19"/>
+      <c r="G1687" s="19"/>
+      <c r="H1687" s="20"/>
+      <c r="I1687" s="20"/>
+      <c r="J1687" s="21"/>
+    </row>
+    <row r="1688" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1688" s="37"/>
+      <c r="C1688" s="18"/>
+      <c r="D1688" s="40"/>
+      <c r="F1688" s="19"/>
+      <c r="G1688" s="19"/>
+      <c r="H1688" s="20"/>
+      <c r="I1688" s="20"/>
+      <c r="J1688" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J162" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J164" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D171">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -34668,7 +34836,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D171">
+  <conditionalFormatting sqref="D173">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
